--- a/artfynd/A 24879-2026 artfynd.xlsx
+++ b/artfynd/A 24879-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1310,6 +1310,1029 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134083243</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58249</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rävslätten, Rävslätten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>499205</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6576669</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134080557</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rävslätten, Rävslätten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>499213</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6576428</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134084140</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57961</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rävslätten, Rävslätten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>499176</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6576390</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134082989</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57961</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rävslätten, Rävslätten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>499283</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6576677</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134083716</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rävslätten, Rävslätten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>499205</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6576669</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134081400</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rävslätten, Rävslätten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>499312</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6576582</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134080509</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58249</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rävslätten, Rävslätten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>499216</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6576424</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134080683</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99082</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rävslätten, Rävslätten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>499228</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6576422</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134083560</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rävslätten, Rävslätten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>499240</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6576605</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24879-2026 artfynd.xlsx
+++ b/artfynd/A 24879-2026 artfynd.xlsx
@@ -1315,7 +1315,7 @@
         <v>134083243</v>
       </c>
       <c r="B7" t="n">
-        <v>58249</v>
+        <v>58250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>134084140</v>
       </c>
       <c r="B9" t="n">
-        <v>57961</v>
+        <v>57962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>134082989</v>
       </c>
       <c r="B10" t="n">
-        <v>57961</v>
+        <v>57962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,48 +1852,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134081400</v>
+        <v>134080509</v>
       </c>
       <c r="B12" t="n">
-        <v>4776</v>
+        <v>58250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100299</v>
+        <v>103012</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rävslätten, Rävslätten, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499312</v>
+        <v>499216</v>
       </c>
       <c r="R12" t="n">
-        <v>6576582</v>
+        <v>6576424</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1927,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1937,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,91 +1948,61 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134080509</v>
+        <v>134080683</v>
       </c>
       <c r="B13" t="n">
-        <v>58249</v>
+        <v>99085</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rävslätten, Rävslätten, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499216</v>
+        <v>499228</v>
       </c>
       <c r="R13" t="n">
-        <v>6576424</v>
+        <v>6576422</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2059,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2069,7 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,10 +2071,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134080683</v>
+        <v>134081400</v>
       </c>
       <c r="B14" t="n">
-        <v>99082</v>
+        <v>4776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,21 +2082,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,13 +2106,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499228</v>
+        <v>499312</v>
       </c>
       <c r="R14" t="n">
-        <v>6576422</v>
+        <v>6576582</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2166,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2176,7 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,16 +2162,41 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 24879-2026 artfynd.xlsx
+++ b/artfynd/A 24879-2026 artfynd.xlsx
@@ -1315,7 +1315,7 @@
         <v>134083243</v>
       </c>
       <c r="B7" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>134084140</v>
       </c>
       <c r="B9" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>134082989</v>
       </c>
       <c r="B10" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>134080509</v>
       </c>
       <c r="B12" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>134080683</v>
       </c>
       <c r="B13" t="n">
-        <v>99085</v>
+        <v>99095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 24879-2026 artfynd.xlsx
+++ b/artfynd/A 24879-2026 artfynd.xlsx
@@ -1964,10 +1964,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134080683</v>
+        <v>134081400</v>
       </c>
       <c r="B13" t="n">
-        <v>99095</v>
+        <v>4776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>100299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1999,13 +1999,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499228</v>
+        <v>499312</v>
       </c>
       <c r="R13" t="n">
-        <v>6576422</v>
+        <v>6576582</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,26 +2055,51 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134081400</v>
+        <v>134080683</v>
       </c>
       <c r="B14" t="n">
-        <v>4776</v>
+        <v>99097</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,21 +2107,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2106,13 +2131,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499312</v>
+        <v>499228</v>
       </c>
       <c r="R14" t="n">
-        <v>6576582</v>
+        <v>6576422</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2141,7 +2166,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2176,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,41 +2187,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 24879-2026 artfynd.xlsx
+++ b/artfynd/A 24879-2026 artfynd.xlsx
@@ -1964,10 +1964,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134081400</v>
+        <v>134080683</v>
       </c>
       <c r="B13" t="n">
-        <v>4776</v>
+        <v>99097</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100299</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1999,13 +1999,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499312</v>
+        <v>499228</v>
       </c>
       <c r="R13" t="n">
-        <v>6576582</v>
+        <v>6576422</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,51 +2055,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134080683</v>
+        <v>134081400</v>
       </c>
       <c r="B14" t="n">
-        <v>99097</v>
+        <v>4776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,21 +2082,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,13 +2106,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499228</v>
+        <v>499312</v>
       </c>
       <c r="R14" t="n">
-        <v>6576422</v>
+        <v>6576582</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2166,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2176,7 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,16 +2162,41 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 24879-2026 artfynd.xlsx
+++ b/artfynd/A 24879-2026 artfynd.xlsx
@@ -1959,48 +1959,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134081400</v>
+        <v>134080509</v>
       </c>
       <c r="B13" t="n">
-        <v>4776</v>
+        <v>58260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100299</v>
+        <v>103012</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rävslätten, Rävslätten, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499312</v>
+        <v>499216</v>
       </c>
       <c r="R13" t="n">
-        <v>6576582</v>
+        <v>6576424</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,7 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,94 +2055,64 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134080509</v>
+        <v>134081400</v>
       </c>
       <c r="B14" t="n">
-        <v>58260</v>
+        <v>4776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103012</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rävslätten, Rävslätten, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499216</v>
+        <v>499312</v>
       </c>
       <c r="R14" t="n">
-        <v>6576424</v>
+        <v>6576582</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2166,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2176,7 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,16 +2162,41 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 24879-2026 artfynd.xlsx
+++ b/artfynd/A 24879-2026 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134080683</v>
+        <v>134081400</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>4776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499228</v>
+        <v>499312</v>
       </c>
       <c r="R12" t="n">
-        <v>6576422</v>
+        <v>6576582</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,16 +1943,41 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2071,10 +2096,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134081400</v>
+        <v>134080683</v>
       </c>
       <c r="B14" t="n">
-        <v>4776</v>
+        <v>99105</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,21 +2107,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2106,13 +2131,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499312</v>
+        <v>499228</v>
       </c>
       <c r="R14" t="n">
-        <v>6576582</v>
+        <v>6576422</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2141,7 +2166,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2176,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,41 +2187,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 24879-2026 artfynd.xlsx
+++ b/artfynd/A 24879-2026 artfynd.xlsx
@@ -675,57 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68302258</v>
+        <v>104164516</v>
       </c>
       <c r="B2" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>3518</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rävslätten, Nrk</t>
+          <t>Rävslätten, öster om, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499425.7554509093</v>
+        <v>499443</v>
       </c>
       <c r="R2" t="n">
-        <v>6576591.01265439</v>
+        <v>6576513</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-09-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-09-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stötte dem vid parti med fuktig granskog.</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,8 +765,14 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Grandominerad blandskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -789,7 +782,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Henrik Josefsson, Lena Björk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -799,16 +792,11 @@
         <v>104164487</v>
       </c>
       <c r="B3" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -847,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499442.6130405907</v>
+        <v>499443</v>
       </c>
       <c r="R3" t="n">
-        <v>6576512.935118986</v>
+        <v>6576513</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,19 +868,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,64 +908,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104164516</v>
+        <v>111860411</v>
       </c>
       <c r="B4" t="n">
-        <v>83136</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3518</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rävslätten, öster om, Nrk</t>
+          <t>Rävslätten, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499442.6130405907</v>
+        <v>499255</v>
       </c>
       <c r="R4" t="n">
-        <v>6576512.935118986</v>
+        <v>6576674</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,22 +984,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växte i vägkanten vid avfarten till torpet.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,11 +1007,6 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Grandominerad blandskog</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1052,71 +1015,55 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henrik Josefsson, Lena Björk</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104164505</v>
+        <v>134082989</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rävslätten, öster om, Nrk</t>
+          <t>Rävslätten, Rävslätten, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499442.6130405907</v>
+        <v>499283</v>
       </c>
       <c r="R5" t="n">
-        <v>6576512.935118986</v>
+        <v>6576677</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1140,27 +1087,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Cirka 5 fruktkroppar.</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,85 +1111,68 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Grandominerad blandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henrik Josefsson, Lena Björk</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111860411</v>
+        <v>134084140</v>
       </c>
       <c r="B6" t="n">
-        <v>90818</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4368</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rävslätten, Nrk</t>
+          <t>Rävslätten, Rävslätten, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499255</v>
+        <v>499176</v>
       </c>
       <c r="R6" t="n">
-        <v>6576674</v>
+        <v>6576390</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1274,17 +1199,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Växte i vägkanten vid avfarten till torpet.</t>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,64 +1223,68 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134083243</v>
+        <v>134139820</v>
       </c>
       <c r="B7" t="n">
-        <v>58260</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rävslätten, Rävslätten, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499205</v>
+        <v>498985</v>
       </c>
       <c r="R7" t="n">
-        <v>6576669</v>
+        <v>6576249</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1377,22 +1311,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1526,53 +1460,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134084140</v>
+        <v>134081400</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>4776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rävslätten, Rävslätten, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499176</v>
+        <v>499312</v>
       </c>
       <c r="R9" t="n">
-        <v>6576390</v>
+        <v>6576582</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1601,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1540,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,48 +1551,73 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134082989</v>
+        <v>134083560</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>4776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1673,13 +1627,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499283</v>
+        <v>499240</v>
       </c>
       <c r="R10" t="n">
-        <v>6576677</v>
+        <v>6576605</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1672,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,16 +1683,41 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1852,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134081400</v>
+        <v>68302258</v>
       </c>
       <c r="B12" t="n">
-        <v>4776</v>
+        <v>57132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,37 +1842,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100299</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rävslätten, Rävslätten, Nrk</t>
+          <t>Rävslätten, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499312</v>
+        <v>499426</v>
       </c>
       <c r="R12" t="n">
-        <v>6576582</v>
+        <v>6576591</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1917,22 +1900,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2017-09-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2017-09-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stötte dem vid parti med fuktig granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,41 +1921,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2096,32 +2049,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134080683</v>
+        <v>134083243</v>
       </c>
       <c r="B14" t="n">
-        <v>99105</v>
+        <v>58260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>103012</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,13 +2084,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499228</v>
+        <v>499205</v>
       </c>
       <c r="R14" t="n">
-        <v>6576422</v>
+        <v>6576669</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2166,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2176,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2203,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134083560</v>
+        <v>134080683</v>
       </c>
       <c r="B15" t="n">
-        <v>4776</v>
+        <v>99112</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,21 +2167,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100299</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2238,13 +2191,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499240</v>
+        <v>499228</v>
       </c>
       <c r="R15" t="n">
-        <v>6576605</v>
+        <v>6576422</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2273,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2283,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,41 +2247,16 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 24879-2026 artfynd.xlsx
+++ b/artfynd/A 24879-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104164516</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104164487</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111860411</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082989</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134084140</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139820</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,6 +1492,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134080557</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1589,6 +1629,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134081400</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1721,6 +1766,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134083560</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1828,6 +1878,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134083716</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1934,6 +1989,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68302258</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2046,6 +2106,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134080509</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2153,6 +2218,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134083243</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2260,8 +2330,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134080683</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>